--- a/01-projetos/01-data-project-foundations/data/input/absenteeism_data_18.xlsx
+++ b/01-projetos/01-data-project-foundations/data/input/absenteeism_data_18.xlsx
@@ -471,11 +471,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>54596</v>
+        <v>30944</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Rebeca Souza</t>
+          <t>Enrico Viana</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -485,31 +485,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Doença</t>
+          <t>Consulta médica</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>45098</v>
+        <v>45106</v>
       </c>
       <c r="G2" t="n">
-        <v>11593.36</v>
+        <v>5603.33</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>76060</v>
+        <v>21513</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Maria Julia Pinto</t>
+          <t>André Ferreira</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>P&amp;D</t>
+          <t>Jurídico</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -518,51 +518,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>45101</v>
+        <v>45098</v>
       </c>
       <c r="G3" t="n">
-        <v>4503.57</v>
+        <v>12102.77</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>40183</v>
+        <v>94032</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Rafaela Cardoso</t>
+          <t>Lorena Almeida</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Recursos Humanos</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Problemas pessoais</t>
+          <t>Viagem de negócios</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>45088</v>
+        <v>45086</v>
       </c>
       <c r="G4" t="n">
-        <v>2947.93</v>
+        <v>10995.74</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>71617</v>
+        <v>98118</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Lorena Almeida</t>
+          <t>Daniel da Cunha</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -572,7 +572,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Doença</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -582,50 +582,50 @@
         <v>45101</v>
       </c>
       <c r="G5" t="n">
-        <v>12126.91</v>
+        <v>10592.65</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>91892</v>
+        <v>17480</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mariane Rocha</t>
+          <t>Sra. Pietra da Cunha</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vendas</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Consulta médica</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>45104</v>
+        <v>45082</v>
       </c>
       <c r="G6" t="n">
-        <v>4196.83</v>
+        <v>10041.72</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>92812</v>
+        <v>75104</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ana Clara Porto</t>
+          <t>Gabriel Vieira</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Vendas</t>
+          <t>Financeiro</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -634,85 +634,85 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>45095</v>
+        <v>45080</v>
       </c>
       <c r="G7" t="n">
-        <v>8678.65</v>
+        <v>7522.77</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>56893</v>
+        <v>99251</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Isis Sales</t>
+          <t>Maysa Ferreira</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Vendas</t>
+          <t>Financeiro</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Consulta médica</t>
+          <t>Doença</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>45086</v>
+        <v>45084</v>
       </c>
       <c r="G8" t="n">
-        <v>11281.05</v>
+        <v>8607.35</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>79830</v>
+        <v>41703</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bernardo da Mota</t>
+          <t>Ana Clara Pinto</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Recursos Humanos</t>
+          <t>Atendimento ao Cliente</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Viagem de negócios</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>45103</v>
+        <v>45101</v>
       </c>
       <c r="G9" t="n">
-        <v>10757.77</v>
+        <v>3823.37</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>98807</v>
+        <v>23722</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cauã Alves</t>
+          <t>Emanuella Cardoso</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Financeiro</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -721,42 +721,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>45096</v>
+        <v>45100</v>
       </c>
       <c r="G10" t="n">
-        <v>2723.27</v>
+        <v>11995.18</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>61634</v>
+        <v>7065</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Noah Campos</t>
+          <t>Davi Lucca Sales</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>P&amp;D</t>
+          <t>Financeiro</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Doença</t>
+          <t>Problemas pessoais</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>45078</v>
+        <v>45091</v>
       </c>
       <c r="G11" t="n">
-        <v>7752.37</v>
+        <v>12314.56</v>
       </c>
     </row>
   </sheetData>
